--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584321.0076373108</v>
+        <v>584321</v>
       </c>
       <c r="R2" t="n">
-        <v>6421633.167960353</v>
+        <v>6421633</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74152880</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51833-2021 artfynd.xlsx
+++ b/artfynd/A 51833-2021 artfynd.xlsx
@@ -675,44 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74152880</v>
+        <v>96460447</v>
       </c>
       <c r="B2" t="n">
-        <v>98589</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>L19 Nygård norra gdn 750 m NO, Sm</t>
+          <t>A51833, Nygård, Gamleby, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584321</v>
+        <v>584154</v>
       </c>
       <c r="R2" t="n">
         <v>6421633</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -736,17 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7G4h 2816. SOM: Dactylorhiza maculata ssp. maculata. LEG: Birger Danielsson</t>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -755,42 +775,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsväg</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>96460481</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584178.7991683237</v>
+        <v>584179</v>
       </c>
       <c r="R3" t="n">
-        <v>6421663.640876411</v>
+        <v>6421664</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,64 +913,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96460447</v>
+        <v>74152880</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A51833, Nygård, Gamleby, Sm</t>
+          <t>L19 Nygård norra gdn 750 m NO, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584154.4215792033</v>
+        <v>584321</v>
       </c>
       <c r="R4" t="n">
-        <v>6421633.381323397</v>
+        <v>6421633</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G4h 2816. SOM: Dactylorhiza maculata ssp. maculata. LEG: Birger Danielsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,22 +993,30 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
